--- a/AAAGameData/DataTables/SummonerSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonerSkillTable.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,9 +46,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -416,23 +419,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="39" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,6 +475,20 @@
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -478,52 +509,122 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>SummonerClass</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>SkillType</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>UnlockTier</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>BranchId</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Cooldown</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>SpiritCost</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>EffectType</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>EffectValue</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RangeType</t>
+          <t>CastRange</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>AreaRadius</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>SpritePath</t>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>DamageCoeff</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>BaseDamage</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>EffectHitType</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>ProjectilePrefabId</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>ProjectileSpeed</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>HitCount</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>BuffIds</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>SelfBuffIds</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Params</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>EffectId</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>HitEffectId</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>EffectSpawnHeight</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>IconId</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>Desc</t>
         </is>
       </c>
     </row>
@@ -551,47 +652,117 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>float[]</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Z3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AB3" s="1" t="inlineStr">
         <is>
           <t>string</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
@@ -603,7 +774,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>技能ID</t>
+          <t>技能唯一ID</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -618,59 +789,129 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>技能类型(1=被动，2=主动)</t>
+          <t>所属召唤师职业 1=狂战 2=术士 3=混沌 4=德鲁伊</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>冷却时间</t>
+          <t>技能类型 1=被动 2=主动</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
+          <t>解锁阶段 1=初始 3=第三阶 4=第四阶 5=第五阶</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>分支ID 0=固定技能 1=路线一 2=路线二</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>冷却时间（秒）</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
           <t>灵力消耗</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>效果类型（1=Buff,2=Debuff,3=伤害,4=治疗）</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>效果值</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>持续时间（0表示条件触发，无持续时间）</t>
-        </is>
-      </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>作用范围</t>
+          <t>持续时间（秒）</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>范围类型（0=作用于自己，1=单体，2=直线，3=群体）</t>
+          <t>施法/生效范围</t>
         </is>
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>AOE半径（0=单体）</t>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>图标路径</t>
+          <t>伤害类型 0=无 1=物理 2=魔法 3=真实</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>伤害系数（基于攻击力/法强 如1.5=150%）</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>基础固定伤害</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>命中类型 0=瞬发 1=近战 2=投射物 3=AoE 4=射线</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>投射物预制体ID（0=无）</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>投射物速度（0=即时命中）</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>命中/触发次数</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>释放时附加到目标的BuffID数组</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>释放时附加到自身的BuffID数组</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>技能专属参数数组（含义由各技能代码定义 见Desc备注）</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="inlineStr">
+        <is>
+          <t>技能特效资源ID</t>
+        </is>
+      </c>
+      <c r="Y4" s="1" t="inlineStr">
+        <is>
+          <t>受击特效资源ID</t>
+        </is>
+      </c>
+      <c r="Z4" s="1" t="inlineStr">
+        <is>
+          <t>特效生成高度偏移</t>
+        </is>
+      </c>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
+          <t>技能图标资源ID</t>
+        </is>
+      </c>
+      <c r="AB4" s="1" t="inlineStr">
+        <is>
+          <t>技能描述</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C5" s="1" t="n"/>
       <c r="D5" s="1" t="inlineStr">
@@ -685,30 +926,354 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>半血时攻速+20%</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>1701</v>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>0.5,0.4,0.15,2.0</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB5" s="1" t="inlineStr">
+        <is>
+          <t>狂战固定被动。Params[0]=友方低血阈值(0.5) Params[1]=自身低血阈值(0.4) Params[2]=基础伤害提升(0.15) Params[3]=翻倍系数(2.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>战意激昂</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>3001,3002</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>20,0.20,0.15</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>2102</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>2103</v>
+      </c>
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>狂战固定主动。Params[0]=HP消耗(20) Params[1]=攻速提升(0.20) Params[2]=伤害提升(0.15)。BuffIds=攻速Buff/伤害Buff ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>暗影咒体</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>0.1,0.8,0.3</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>2201</v>
+      </c>
+      <c r="AB7" s="1" t="inlineStr">
+        <is>
+          <t>术士固定被动。Params[0]=伤害提升(0.1) Params[1]=受伤诅咒概率(0.8) Params[2]=造伤诅咒概率(0.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>生命虹吸</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>0,0.20,0.15</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>2202</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>2203</v>
+      </c>
+      <c r="AB8" s="1" t="inlineStr">
+        <is>
+          <t>术士固定主动。Params[0]=每秒吸血量（0=按法强计算）Params[1]=目标虚弱移速降低(0.20) Params[2]=虚弱攻速降低(0.15)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonerSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonerSkillTable.xlsx
@@ -442,8 +442,8 @@
     <col width="24" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="46" customWidth="1" min="22" max="22"/>
     <col width="50" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
@@ -481,8 +481,8 @@
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="1" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
       <c r="W1" s="2" t="n"/>
       <c r="X1" s="1" t="n"/>
       <c r="Y1" s="1" t="n"/>
@@ -587,14 +587,14 @@
           <t>HitCount</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>BuffIds</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>SelfBuffIds</t>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>InstantBuffs</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>HitBuffs</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -725,14 +725,14 @@
           <t>int</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>int[]</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>int[]</t>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -867,14 +867,14 @@
           <t>命中/触发次数</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>释放时附加到目标的BuffID数组</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>释放时附加到自身的BuffID数组</t>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>释放/条件触发时施加的Buff列表，格式"buffId:targetType,..."。targetType:1=召唤师自身 2=全体友方(不含召唤师) 3=全体友方(含召唤师) 4=全体敌方 5=命中目标(单体)</t>
+        </is>
+      </c>
+      <c r="V4" s="1" t="inlineStr">
+        <is>
+          <t>命中目标时施加的Buff列表，格式同InstantBuffs</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -967,19 +967,19 @@
       <c r="T5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" s="1" t="inlineStr">
+        <is>
+          <t>4003:3</t>
+        </is>
+      </c>
+      <c r="V5" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0.5,0.4,0.15,2.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" s="1" t="n">
@@ -992,11 +992,11 @@
         <v>0</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>2101</v>
+        <v>1701</v>
       </c>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>狂战固定被动。Params[0]=友方低血阈值(0.5) Params[1]=自身低血阈值(0.4) Params[2]=基础伤害提升(0.15) Params[3]=翻倍系数(2.0)</t>
+          <t>狂战固定被动。条件触发：战场有友方HP&lt;Params[0]时，InstantBuffs施加（4003→全体友方含召唤师）；BerserkerRageBuff自动检测目标是否为召唤师并应用30%伤害加成。条件解除时移除</t>
         </is>
       </c>
     </row>
@@ -1059,19 +1059,19 @@
       <c r="T6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>3001,3002</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U6" s="1" t="inlineStr">
+        <is>
+          <t>4001:3</t>
+        </is>
+      </c>
+      <c r="V6" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,0.20,0.15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="X6" s="1" t="n">
@@ -1084,11 +1084,11 @@
         <v>0</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>2103</v>
+        <v>1702</v>
       </c>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>狂战固定主动。Params[0]=HP消耗(20) Params[1]=攻速提升(0.20) Params[2]=伤害提升(0.15)。BuffIds=攻速Buff/伤害Buff ID</t>
+          <t>狂战固定主动。Params[0]=HP消耗(20)。扣除召唤师HP后，InstantBuffs施加战意激昂Buff（攻速+20%伤害+15%）到全体友方（含召唤师），持续10秒</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       <c r="T7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V7" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1243,14 +1243,14 @@
       <c r="T8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U8" s="1" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="V8" s="1" t="inlineStr">
+        <is>
+          <t>3003:5</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>术士固定主动。Params[0]=每秒吸血量（0=按法强计算）Params[1]=目标虚弱移速降低(0.20) Params[2]=虚弱攻速降低(0.15)</t>
+          <t>术士固定主动。命中时HitBuffs施加3003流血到命中目标。Params[0]=每秒吸血量 Params[1]=虚弱移速降低 Params[2]=虚弱攻速降低</t>
         </is>
       </c>
     </row>

--- a/AAAGameData/DataTables/SummonerSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonerSkillTable.xlsx
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="AA13" s="3">
-        <v>1801</v>
+        <v>1711</v>
       </c>
       <c r="AB13" s="1" t="s">
         <v>91</v>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
-        <v>1802</v>
+        <v>1712</v>
       </c>
       <c r="AB14" s="1" t="s">
         <v>94</v>

--- a/AAAGameData/DataTables/SummonerSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonerSkillTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="96">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>SkillType</t>
   </si>
   <si>
+    <t>TargetDeadState</t>
+  </si>
+  <si>
     <t>UnlockTier</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
     <t>技能类型 1=被动 2=主动</t>
   </si>
   <si>
+    <t>作用目标存活状态</t>
+  </si>
+  <si>
     <t>解锁阶段 1=初始 3=第三阶 4=第四阶 5=第五阶</t>
   </si>
   <si>
@@ -209,46 +215,43 @@
     <t>狂怒之心</t>
   </si>
   <si>
+    <t>{4002:3}</t>
+  </si>
+  <si>
+    <t>0.5,0.4,0.15</t>
+  </si>
+  <si>
+    <t>所有友方的生命值低于50%时，其所造成的伤害提升15%。当玩家生命值低于40%时，自身造成的伤害再次提升15%，并且全体召唤物的伤害提升效果翻倍。</t>
+  </si>
+  <si>
+    <t>战意激昂</t>
+  </si>
+  <si>
+    <t>{4001:3}</t>
+  </si>
+  <si>
+    <t>20,0.2,0.15</t>
+  </si>
+  <si>
+    <t>玩家消耗一定生命值（20点），短时间（持续10s）内大幅提升场上召唤物的攻击速度（+20%）和伤害（+15%）。</t>
+  </si>
+  <si>
+    <t>王者号令</t>
+  </si>
+  <si>
+    <t>{4004:3}</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>4003:3</t>
-  </si>
-  <si>
-    <t>0.5,0.4,0.15</t>
-  </si>
-  <si>
-    <t>所有友方的生命值低于50%时，其所造成的伤害提升15%。当玩家生命值低于40%时，自身造成的伤害再次提升15%，并且全体召唤物的伤害提升效果翻倍。</t>
-  </si>
-  <si>
-    <t>战意激昂</t>
-  </si>
-  <si>
-    <t>4001:3</t>
-  </si>
-  <si>
-    <t>20,0.2,0.15</t>
-  </si>
-  <si>
-    <t>玩家消耗一定生命值（20点），短时间（持续10s）内大幅提升场上召唤物的攻击速度（+20%）和伤害（+15%）。</t>
-  </si>
-  <si>
-    <t>王者号令</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4004:3</t>
-  </si>
-  <si>
     <t>命令场上所有召唤物立即对目标敌人发起一次强力普攻（此次攻击伤害增加50%），并嘲讽附近400码内的敌人，持续一定时间（15s）。</t>
   </si>
   <si>
     <t>钢铁洪流</t>
   </si>
   <si>
-    <t>4005:3</t>
+    <t>{4005:3}</t>
   </si>
   <si>
     <t>4,0.25,0.3</t>
@@ -260,7 +263,7 @@
     <t>天灾降临</t>
   </si>
   <si>
-    <t>4006:3</t>
+    <t>{4006:3}</t>
   </si>
   <si>
     <t>在指定区域召唤一场持续性的战争风暴，对范围内的所有敌人持续造成巨额伤害，并为范围内的所有友方棋子提供巨额护盾和生命偷取效果。战争风暴效果持续5s。</t>
@@ -269,7 +272,7 @@
     <t>寂灭斩</t>
   </si>
   <si>
-    <t>4007:5</t>
+    <t>{4007:5}</t>
   </si>
   <si>
     <t>对单个敌人发动一次超高伤害的斩击，若目标被击败，则重置此技能冷却时间。</t>
@@ -278,7 +281,7 @@
     <t>孤影</t>
   </si>
   <si>
-    <t>4008:1</t>
+    <t>{4008:1}</t>
   </si>
   <si>
     <t>当身边没有其他友方棋子时，自身造成的所有伤害大幅提升，并获得高额闪避率。</t>
@@ -287,7 +290,7 @@
     <t>裁决之刻</t>
   </si>
   <si>
-    <t>4009:5</t>
+    <t>{4009:5}</t>
   </si>
   <si>
     <t>标记一名敌人，在短暂延迟后，对其发动一次无视大量百分比防御（70%）的终极斩击。如果此击击败目标，将对所有其他敌人造成一次巨大的范围恐惧效果。</t>
@@ -296,7 +299,7 @@
     <t>暗影咒体</t>
   </si>
   <si>
-    <t>4010:3</t>
+    <t>{4010:3}</t>
   </si>
   <si>
     <t>0.8,0.3</t>
@@ -308,7 +311,7 @@
     <t>生命虹吸</t>
   </si>
   <si>
-    <t>4011:4</t>
+    <t>{4011:4}</t>
   </si>
   <si>
     <t>选择一名敌人，在一定范围内，持续从对方身上吸取生命值。并对自己和一定范围内生命值最少的友方进行等量治疗。被吸取生命值的敌人会进入虚弱状态（移速-20%，攻速-15%）。</t>
@@ -932,15 +935,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1289,8 +1289,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1298,30 +1298,31 @@
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="8" width="37" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="36" customWidth="1"/>
-    <col min="15" max="15" width="40" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="46" customWidth="1"/>
-    <col min="18" max="18" width="24" customWidth="1"/>
-    <col min="19" max="19" width="26" customWidth="1"/>
-    <col min="20" max="20" width="15" customWidth="1"/>
-    <col min="21" max="21" width="50" customWidth="1"/>
-    <col min="22" max="22" width="46" customWidth="1"/>
-    <col min="23" max="23" width="53.1111111111111" customWidth="1"/>
-    <col min="24" max="25" width="16" customWidth="1"/>
-    <col min="26" max="26" width="19" customWidth="1"/>
-    <col min="27" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="160.777777777778" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="9" max="9" width="37" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="36" customWidth="1"/>
+    <col min="16" max="16" width="40" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="46" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
+    <col min="21" max="21" width="15" customWidth="1"/>
+    <col min="22" max="22" width="50" customWidth="1"/>
+    <col min="23" max="23" width="46" customWidth="1"/>
+    <col min="24" max="24" width="50" customWidth="1"/>
+    <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="19" customWidth="1"/>
+    <col min="28" max="28" width="16" customWidth="1"/>
+    <col min="29" max="29" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1348,14 +1349,15 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="2"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1420,10 +1422,10 @@
       <c r="V2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -1438,185 +1440,194 @@
       <c r="AB2" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC2" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:29">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="Z3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="AB3" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AC3" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" ht="57.6" spans="1:28">
+    <row r="4" ht="54" spans="1:29">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="X4" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="Y4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:28">
+    <row r="5" ht="15" customHeight="1" spans="1:29">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1625,11 +1636,11 @@
         <v>1</v>
       </c>
       <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
@@ -1666,17 +1677,15 @@
       <c r="T5" s="1">
         <v>0</v>
       </c>
-      <c r="U5" s="1" t="s">
-        <v>60</v>
+      <c r="U5" s="1">
+        <v>0</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="W5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="X5" s="1">
-        <v>0</v>
+      <c r="W5" s="1"/>
+      <c r="X5" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
@@ -1685,20 +1694,23 @@
         <v>0</v>
       </c>
       <c r="AA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1">
         <v>1701</v>
       </c>
-      <c r="AB5" s="1" t="s">
-        <v>63</v>
+      <c r="AC5" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:28">
+    <row r="6" ht="15" customHeight="1" spans="1:29">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1707,23 +1719,23 @@
         <v>2</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
       <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>10</v>
       </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
       <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>10</v>
       </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
@@ -1748,17 +1760,15 @@
       <c r="T6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>60</v>
+      <c r="U6" s="1">
+        <v>0</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="W6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="X6" s="1">
-        <v>0</v>
+      <c r="W6" s="1"/>
+      <c r="X6" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -1766,21 +1776,24 @@
       <c r="Z6" s="1">
         <v>0</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
         <v>1702</v>
       </c>
-      <c r="AB6" s="1" t="s">
-        <v>67</v>
+      <c r="AC6" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:28">
+    <row r="7" ht="15" customHeight="1" spans="1:29">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>103</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1789,29 +1802,29 @@
         <v>2</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>3</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>15</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
       <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <v>15</v>
       </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
       <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
         <v>400</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
       <c r="O7" s="1">
         <v>0</v>
       </c>
@@ -1822,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
         <v>0</v>
@@ -1830,17 +1843,15 @@
       <c r="T7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>69</v>
+      <c r="U7" s="1">
+        <v>0</v>
       </c>
       <c r="V7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X7" s="1">
-        <v>0</v>
+      <c r="W7" s="1"/>
+      <c r="X7" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -1848,21 +1859,24 @@
       <c r="Z7" s="1">
         <v>0</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
         <v>1703</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>71</v>
+      <c r="AC7" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:28">
+    <row r="8" ht="15" customHeight="1" spans="1:29">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>104</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1871,14 +1885,14 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>4</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
       <c r="J8" s="1">
         <v>0</v>
       </c>
@@ -1912,17 +1926,15 @@
       <c r="T8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>60</v>
+      <c r="U8" s="1">
+        <v>0</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="W8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="X8" s="1">
-        <v>0</v>
+      <c r="W8" s="1"/>
+      <c r="X8" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -1930,21 +1942,24 @@
       <c r="Z8" s="1">
         <v>0</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
         <v>1704</v>
       </c>
-      <c r="AB8" s="1" t="s">
-        <v>75</v>
+      <c r="AC8" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:28">
+    <row r="9" ht="15" customHeight="1" spans="1:29">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>105</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1953,32 +1968,32 @@
         <v>2</v>
       </c>
       <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>5</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>20</v>
       </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
       <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
         <v>5</v>
       </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
       <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>600</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>3</v>
       </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
       <c r="P9" s="1">
         <v>0</v>
       </c>
@@ -1986,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1">
         <v>0</v>
@@ -1994,17 +2009,15 @@
       <c r="T9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>69</v>
+      <c r="U9" s="1">
+        <v>0</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X9" s="1">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="W9" s="1"/>
+      <c r="X9" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
@@ -2012,21 +2025,24 @@
       <c r="Z9" s="1">
         <v>0</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
         <v>1705</v>
       </c>
-      <c r="AB9" s="1" t="s">
-        <v>78</v>
+      <c r="AC9" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:28">
+    <row r="10" ht="15" customHeight="1" spans="1:29">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>106</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2035,17 +2051,17 @@
         <v>2</v>
       </c>
       <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>12</v>
       </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
@@ -2059,16 +2075,16 @@
         <v>0</v>
       </c>
       <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
         <v>1</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>1.8</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
       <c r="R10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="1">
         <v>0</v>
@@ -2076,17 +2092,15 @@
       <c r="T10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>69</v>
+      <c r="U10" s="1">
+        <v>0</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X10" s="1">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="X10" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
@@ -2094,21 +2108,24 @@
       <c r="Z10" s="1">
         <v>0</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
         <v>1706</v>
       </c>
-      <c r="AB10" s="1" t="s">
-        <v>81</v>
+      <c r="AC10" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:28">
+    <row r="11" ht="15" customHeight="1" spans="1:29">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>107</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2117,14 +2134,14 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>4</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
@@ -2158,17 +2175,15 @@
       <c r="T11" s="1">
         <v>0</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>60</v>
+      <c r="U11" s="1">
+        <v>0</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X11" s="1">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="W11" s="1"/>
+      <c r="X11" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -2176,21 +2191,24 @@
       <c r="Z11" s="1">
         <v>0</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1">
         <v>1707</v>
       </c>
-      <c r="AB11" s="1" t="s">
-        <v>84</v>
+      <c r="AC11" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:28">
+    <row r="12" ht="15" customHeight="1" spans="1:29">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>108</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2199,17 +2217,17 @@
         <v>2</v>
       </c>
       <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>5</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>2</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>18</v>
       </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
       <c r="K12" s="1">
         <v>0</v>
       </c>
@@ -2223,14 +2241,14 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
         <v>3</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>2</v>
       </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
       <c r="R12" s="1">
         <v>0</v>
       </c>
@@ -2240,17 +2258,15 @@
       <c r="T12" s="1">
         <v>0</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>69</v>
+      <c r="U12" s="1">
+        <v>0</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X12" s="1">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="X12" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -2258,21 +2274,24 @@
       <c r="Z12" s="1">
         <v>0</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
         <v>1708</v>
       </c>
-      <c r="AB12" s="1" t="s">
-        <v>87</v>
+      <c r="AC12" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:28">
+    <row r="13" ht="15" customHeight="1" spans="1:29">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>201</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -2281,11 +2300,11 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>1</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
@@ -2322,17 +2341,15 @@
       <c r="T13" s="1">
         <v>0</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>60</v>
+      <c r="U13" s="1">
+        <v>0</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="X13" s="1">
-        <v>0</v>
+      <c r="W13" s="1"/>
+      <c r="X13" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
@@ -2340,21 +2357,24 @@
       <c r="Z13" s="1">
         <v>0</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
         <v>1711</v>
       </c>
-      <c r="AB13" s="1" t="s">
-        <v>91</v>
+      <c r="AC13" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:28">
+    <row r="14" ht="15" customHeight="1" spans="1:29">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>202</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -2363,40 +2383,40 @@
         <v>2</v>
       </c>
       <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>1</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
       <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
         <v>8</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>30</v>
       </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
       <c r="L14" s="1">
         <v>0</v>
       </c>
       <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
         <v>600</v>
       </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
       <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
         <v>2</v>
       </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
       <c r="Q14" s="1">
         <v>0</v>
       </c>
       <c r="R14" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" s="1">
         <v>0</v>
@@ -2404,17 +2424,15 @@
       <c r="T14" s="1">
         <v>0</v>
       </c>
-      <c r="U14" s="1" t="s">
-        <v>69</v>
+      <c r="U14" s="1">
+        <v>0</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="W14" s="1"/>
+      <c r="X14" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="Y14" s="1">
         <v>0</v>
@@ -2422,11 +2440,14 @@
       <c r="Z14" s="1">
         <v>0</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
         <v>1712</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>94</v>
+      <c r="AC14" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
